--- a/paper-data/2026-10-22/journal.xlsx
+++ b/paper-data/2026-10-22/journal.xlsx
@@ -1467,7 +1467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1505,6 +1505,106 @@
         <is>
           <t>rule_changes</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>976.9299999999999</v>
+      </c>
+      <c r="C2" t="n">
+        <v>976.9299999999999</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-5.16</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>12:32</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>976.9299999999999</v>
+      </c>
+      <c r="C3" t="n">
+        <v>976.9299999999999</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-5.16</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>976.9299999999999</v>
+      </c>
+      <c r="C4" t="n">
+        <v>976.9299999999999</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-5.16</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>3</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>976.9299999999999</v>
+      </c>
+      <c r="C5" t="n">
+        <v>976.9299999999999</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-5.16</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1553,7 +1653,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-22 11:30:27</t>
+          <t>2026-10-22 15:00:21</t>
         </is>
       </c>
     </row>
